--- a/Backend/kksDb.xlsx
+++ b/Backend/kksDb.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/60e0330620d01d27/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/60E0330620D01D27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{1A178DB5-950C-4014-9D24-14DDAEDCDFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33F06B3F-E1CB-46D3-BCF5-A81918B707AB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{33B6E0A0-7F58-40E8-8906-C489539DF7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{44871C58-1648-4DDE-9017-F1EF67E6E9DC}"/>
   </bookViews>
@@ -36,19 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>KKS/25-26/ALA/001</t>
-  </si>
-  <si>
-    <t>KKS/25-26/ALA/002</t>
-  </si>
-  <si>
-    <t>KKS/25-26/ALA/003</t>
-  </si>
-  <si>
-    <t>KKS/25-26/ALA/004</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Vijay</t>
   </si>
@@ -56,18 +44,6 @@
     <t>na23b021@smail.iitm.ac.in</t>
   </si>
   <si>
-    <t>Aravind</t>
-  </si>
-  <si>
-    <t>na23b020@smail.iitm.ac.in</t>
-  </si>
-  <si>
-    <t>na23b005@smail.iitm.ac.in</t>
-  </si>
-  <si>
-    <t>Urumese</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -77,28 +53,13 @@
     <t>email</t>
   </si>
   <si>
-    <t>Rashid</t>
-  </si>
-  <si>
-    <t>na23b034@smail,iitm.ac.in</t>
-  </si>
-  <si>
     <t>KKS/25-26/ALA/005</t>
   </si>
   <si>
-    <t>KKS/25-26/ALA/006</t>
-  </si>
-  <si>
-    <t>urumesejoy11@gmail.com</t>
-  </si>
-  <si>
-    <t>pianoking636@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urumese </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aravind </t>
+    <t>count</t>
+  </si>
+  <si>
+    <t>kksid</t>
   </si>
 </sst>
 </file>
@@ -239,10 +200,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -562,102 +519,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36560C4A-060E-4C99-8429-126517356CA3}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.5546875" customWidth="1"/>
     <col min="2" max="2" width="17.77734375" customWidth="1"/>
     <col min="3" max="3" width="29.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" customWidth="1"/>
+    <col min="5" max="5" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
       <c r="C2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="E2">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>18</v>
-      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3"/>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1"/>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1"/>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{CE9DE46E-DFBB-43BD-A13E-D0E7012A9428}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{853E6B28-CD7D-46B8-8BAE-5E9C2EA172E9}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{1355FAA8-BB27-4B4A-9735-0DCF9E14F25C}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{662AE871-E688-4E15-B501-2883612B28AE}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{F723B1C6-C4D3-4718-A73E-192C9F490DCE}"/>
-    <hyperlink ref="C7" r:id="rId6" xr:uid="{5BF437B3-E555-4BDF-A300-8A11D90272D3}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{05DEFA8F-8C30-4F61-B3A2-FB79BA383302}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId7"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Backend/kksDb.xlsx
+++ b/Backend/kksDb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/60E0330620D01D27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{33B6E0A0-7F58-40E8-8906-C489539DF7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{6FA7DF59-92E9-46A4-9CD7-850D47FDF5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{44871C58-1648-4DDE-9017-F1EF67E6E9DC}"/>
   </bookViews>
@@ -38,12 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>Vijay</t>
-  </si>
-  <si>
-    <t>na23b021@smail.iitm.ac.in</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -53,13 +47,19 @@
     <t>email</t>
   </si>
   <si>
-    <t>KKS/25-26/ALA/005</t>
+    <t>KKS/25-26/ALA/006</t>
   </si>
   <si>
     <t>count</t>
   </si>
   <si>
     <t>kksid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test </t>
+  </si>
+  <si>
+    <t>vijay762005@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -531,42 +531,39 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-      <c r="C3" s="4"/>
-    </row>
+    </row>
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="C4" s="4"/>
@@ -589,7 +586,7 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{05DEFA8F-8C30-4F61-B3A2-FB79BA383302}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{CFF9B27B-C195-4370-A9E5-361EE4F6B449}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/Backend/kksDb.xlsx
+++ b/Backend/kksDb.xlsx
@@ -1,37 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/60E0330620D01D27/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{6FA7DF59-92E9-46A4-9CD7-850D47FDF5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{44871C58-1648-4DDE-9017-F1EF67E6E9DC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -47,51 +25,45 @@
     <t>email</t>
   </si>
   <si>
+    <t>kksid</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test </t>
+  </si>
+  <si>
+    <t>vijay762005@gmail.com</t>
+  </si>
+  <si>
     <t>KKS/25-26/ALA/006</t>
-  </si>
-  <si>
-    <t>count</t>
-  </si>
-  <si>
-    <t>kksid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test </t>
-  </si>
-  <si>
-    <t>vijay762005@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF434343"/>
       <sz val="10"/>
-      <color rgb="FF434343"/>
       <name val="Roboto"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -103,13 +75,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF6F8F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6F8F9"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -120,21 +92,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF284E3F"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF6F8F9"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -167,26 +124,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF284E3F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -518,9 +488,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36560C4A-060E-4C99-8429-126517356CA3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="32.5546875" customWidth="1"/>
     <col min="2" max="2" width="17.77734375" customWidth="1"/>
@@ -529,7 +499,7 @@
     <col min="5" max="5" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -540,55 +510,54 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
+    <row r="2" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" t="s">
         <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1"/>
-      <c r="C5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1"/>
-      <c r="C7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{CFF9B27B-C195-4370-A9E5-361EE4F6B449}"/>
+    <hyperlink ref="C2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>